--- a/identity-mapping-workbook.xlsx
+++ b/identity-mapping-workbook.xlsx
@@ -478,7 +478,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DemandRange — identity mapping workbook</t>
+          <t>Demand Range — identity mapping workbook</t>
         </is>
       </c>
     </row>
